--- a/output/roomself_excel/8205.xlsx
+++ b/output/roomself_excel/8205.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>159980</v>
+        <v>98404</v>
       </c>
       <c r="D2" t="n">
-        <v>3204</v>
+        <v>2516</v>
       </c>
       <c r="E2" t="n">
-        <v>630</v>
+        <v>337</v>
       </c>
       <c r="F2" t="n">
-        <v>405</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>98404</v>
+        <v>45922</v>
       </c>
       <c r="D3" t="n">
-        <v>2516</v>
+        <v>2036</v>
       </c>
       <c r="E3" t="n">
-        <v>630</v>
+        <v>281</v>
       </c>
       <c r="F3" t="n">
-        <v>337</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>45922</v>
+        <v>159980</v>
       </c>
       <c r="D4" t="n">
-        <v>2036</v>
+        <v>3204</v>
       </c>
       <c r="E4" t="n">
-        <v>540</v>
+        <v>473</v>
       </c>
       <c r="F4" t="n">
-        <v>167</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5">
@@ -542,10 +542,10 @@
         <v>1316</v>
       </c>
       <c r="E5" t="n">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="F5" t="n">
-        <v>179</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/8205.xlsx
+++ b/output/roomself_excel/8205.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>2516</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>337</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>31</v>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>292</v>
+      </c>
+      <c r="J2" t="n">
+        <v>24</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +551,31 @@
       <c r="D3" t="n">
         <v>2036</v>
       </c>
-      <c r="E3" t="n">
-        <v>281</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>157</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>237</v>
+      </c>
+      <c r="J3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +592,38 @@
       <c r="D4" t="n">
         <v>3204</v>
       </c>
-      <c r="E4" t="n">
-        <v>473</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>405</v>
+        <v>380</v>
+      </c>
+      <c r="G4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>421</v>
+      </c>
+      <c r="J4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>234</v>
+      </c>
+      <c r="M4" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +641,31 @@
       <c r="D5" t="n">
         <v>1316</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>115</v>
+      </c>
+      <c r="G5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>206</v>
       </c>
-      <c r="F5" t="n">
+      <c r="J5" t="n">
         <v>22</v>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
